--- a/Inam_Restaurant_RTM.xlsx
+++ b/Inam_Restaurant_RTM.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RTM'!$A$3:$H$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RTM'!$A$3:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,9 @@
     <font>
       <b val="1"/>
       <color rgb="00548235"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
     </font>
   </fonts>
   <fills count="8">
@@ -123,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -159,6 +162,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -526,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -537,6 +543,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -594,6 +601,11 @@
           <t>Defect ID</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Execution Method</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -636,6 +648,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -678,6 +695,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="36" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -720,6 +742,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="36" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -762,6 +789,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="36" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -804,6 +836,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="36" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -846,6 +883,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="36" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -888,6 +930,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="36" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -930,6 +977,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="36" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -972,6 +1024,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="36" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1014,6 +1071,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I13" s="11" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="36" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1056,6 +1118,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I14" s="11" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="36" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1098,6 +1165,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I15" s="11" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="36" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1140,6 +1212,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="36" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1182,6 +1259,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="36" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1224,6 +1306,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="36" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
@@ -1266,6 +1353,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="36" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
@@ -1308,6 +1400,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="36" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
@@ -1350,6 +1447,11 @@
           <t>BUG-001</t>
         </is>
       </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="36" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
@@ -1392,6 +1494,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="36" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
@@ -1434,6 +1541,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="36" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
@@ -1476,6 +1588,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="36" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
@@ -1518,6 +1635,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="36" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
@@ -1560,6 +1682,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
@@ -1602,6 +1729,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -1644,6 +1776,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
@@ -1686,6 +1823,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="36" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -1728,6 +1870,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="36" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
@@ -1770,6 +1917,11 @@
           <t>BUG-002</t>
         </is>
       </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
@@ -1812,6 +1964,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
@@ -1854,6 +2011,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
@@ -1896,6 +2058,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
@@ -1938,6 +2105,11 @@
           <t>BUG-003</t>
         </is>
       </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
@@ -1980,6 +2152,11 @@
           <t>BUG-004</t>
         </is>
       </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
@@ -2022,6 +2199,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
@@ -2064,6 +2246,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
@@ -2106,6 +2293,11 @@
           <t>BUG-005</t>
         </is>
       </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="36" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
@@ -2148,6 +2340,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="36" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
@@ -2190,6 +2387,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="36" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
@@ -2232,6 +2434,11 @@
           <t>BUG-006</t>
         </is>
       </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="A43" s="4" t="inlineStr">
@@ -2274,6 +2481,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
@@ -2316,6 +2528,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
@@ -2358,9 +2575,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H45"/>
+  <autoFilter ref="A3:I45"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
